--- a/test/fixtures/xlsx/04_inline_string.xlsx
+++ b/test/fixtures/xlsx/04_inline_string.xlsx
@@ -5,4 +5,35 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline text</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>